--- a/datasets/radio_sources_EoR.xlsx
+++ b/datasets/radio_sources_EoR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tomas Soltinsky\Documents\astrophysics\website\datasets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tomas\Documents\astrophysics\website\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E41441-FF7E-4A77-ABA2-2BF425038924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE70B3BD-93F4-48C8-9F94-EB0BE93674C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hárok1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -248,10 +251,10 @@
     <t>Drouart+20</t>
   </si>
   <si>
-    <t>J1530+1049</t>
-  </si>
-  <si>
-    <t>Saxena+18</t>
+    <t>MGT J10000+02225</t>
+  </si>
+  <si>
+    <t>Varadaraj+26</t>
   </si>
 </sst>
 </file>
@@ -294,7 +297,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normálna" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -310,7 +313,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motív Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -627,16 +630,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" customWidth="1"/>
-    <col min="4" max="4" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="17.5546875" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" customWidth="1"/>
+    <col min="1" max="1" width="16.6328125" customWidth="1"/>
+    <col min="3" max="3" width="13.90625" customWidth="1"/>
+    <col min="4" max="4" width="22.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="17.54296875" customWidth="1"/>
+    <col min="8" max="8" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -659,7 +662,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -676,7 +679,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -693,7 +696,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -710,7 +713,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -733,7 +736,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -750,7 +753,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -773,7 +776,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -796,7 +799,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -814,7 +817,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -828,7 +831,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -845,7 +848,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -863,7 +866,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -883,7 +886,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -903,7 +906,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -926,7 +929,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -943,7 +946,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -960,7 +963,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -977,7 +980,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -994,7 +997,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1008,7 +1011,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1028,7 +1031,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -1051,7 +1054,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1068,7 +1071,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -1079,7 +1082,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -1102,7 +1105,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -1125,7 +1128,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1148,60 +1151,57 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>70</v>
-      </c>
-      <c r="B28">
-        <v>5.72</v>
-      </c>
-      <c r="C28">
-        <v>174.88</v>
-      </c>
-      <c r="D28">
-        <v>-1.4</v>
+        <v>59</v>
+      </c>
+      <c r="B28" s="1">
+        <v>5.718</v>
       </c>
       <c r="E28" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="1">
-        <v>5.718</v>
+        <v>20</v>
+      </c>
+      <c r="B29">
+        <v>5.69</v>
+      </c>
+      <c r="C29">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="D29">
+        <v>-0.04</v>
       </c>
       <c r="E29" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="F29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B30">
-        <v>5.69</v>
-      </c>
-      <c r="C30">
-        <v>0.48499999999999999</v>
+        <v>5.68</v>
       </c>
       <c r="D30">
-        <v>-0.04</v>
+        <v>-0.75</v>
       </c>
       <c r="E30" t="s">
-        <v>14</v>
-      </c>
-      <c r="F30" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B31">
-        <v>5.68</v>
+        <v>5.63</v>
       </c>
       <c r="D31">
         <v>-0.75</v>
@@ -1210,117 +1210,117 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="B32">
-        <v>5.63</v>
+        <v>5.62</v>
+      </c>
+      <c r="C32">
+        <v>1.22</v>
       </c>
       <c r="D32">
-        <v>-0.75</v>
+        <v>-0.23</v>
       </c>
       <c r="E32" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="F32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33">
-        <v>5.62</v>
+        <v>60</v>
+      </c>
+      <c r="B33" s="1">
+        <v>5.6059999999999999</v>
       </c>
       <c r="C33">
-        <v>1.22</v>
+        <v>29.5</v>
       </c>
       <c r="D33">
-        <v>-0.23</v>
+        <v>-0.27</v>
       </c>
       <c r="E33" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="F33" t="s">
-        <v>16</v>
-      </c>
-      <c r="G33" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B34" s="1">
-        <v>5.6059999999999999</v>
+        <v>5.58</v>
       </c>
       <c r="C34">
-        <v>29.5</v>
+        <v>7.46</v>
       </c>
       <c r="D34">
-        <v>-0.27</v>
+        <v>-0.4</v>
       </c>
       <c r="E34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F34" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B35" s="1">
-        <v>5.58</v>
+        <v>5.57</v>
       </c>
       <c r="C35">
-        <v>7.46</v>
+        <v>43.16</v>
       </c>
       <c r="D35">
-        <v>-0.4</v>
+        <v>-0.65</v>
       </c>
       <c r="E35" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B36" s="1">
-        <v>5.57</v>
+        <v>5.55</v>
       </c>
       <c r="C36">
-        <v>43.16</v>
+        <v>899.82</v>
       </c>
       <c r="D36">
-        <v>-0.65</v>
+        <v>-1.18</v>
       </c>
       <c r="E36" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B37" s="1">
-        <v>5.55</v>
-      </c>
-      <c r="C37">
-        <v>899.82</v>
+        <v>5.5446999999999997</v>
       </c>
       <c r="D37">
-        <v>-1.18</v>
+        <v>-1.68</v>
       </c>
       <c r="E37" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G34">
-    <sortCondition descending="1" ref="B1:B34"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G33">
+    <sortCondition descending="1" ref="B1:B33"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/datasets/radio_sources_EoR.xlsx
+++ b/datasets/radio_sources_EoR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tomas\Documents\astrophysics\website\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE70B3BD-93F4-48C8-9F94-EB0BE93674C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD83C3D8-B049-4BEF-AB9D-8D15856B6EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hárok1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="146">
   <si>
     <t>name</t>
   </si>
@@ -255,6 +255,228 @@
   </si>
   <si>
     <t>Varadaraj+26</t>
+  </si>
+  <si>
+    <t>RA (hh:mm:ss)</t>
+  </si>
+  <si>
+    <t>04:10:09.05</t>
+  </si>
+  <si>
+    <t>09:58:58.27</t>
+  </si>
+  <si>
+    <t>-01°39'19.88''</t>
+  </si>
+  <si>
+    <t>+01°39'20.02''</t>
+  </si>
+  <si>
+    <t>11:29:24.08</t>
+  </si>
+  <si>
+    <t>+18°46'38.58''</t>
+  </si>
+  <si>
+    <t>13:50:23.60</t>
+  </si>
+  <si>
+    <t>+37°48'35.67''</t>
+  </si>
+  <si>
+    <t>08:36:43.86</t>
+  </si>
+  <si>
+    <t>+00°54'53.23''</t>
+  </si>
+  <si>
+    <t>DEC</t>
+  </si>
+  <si>
+    <t>23:36:24.69</t>
+  </si>
+  <si>
+    <t>23:18:18.30</t>
+  </si>
+  <si>
+    <t>08:03:05.42</t>
+  </si>
+  <si>
+    <t>11:33:50.42</t>
+  </si>
+  <si>
+    <t>14:29:52.17</t>
+  </si>
+  <si>
+    <t>02:27:43.32</t>
+  </si>
+  <si>
+    <t>03:20:21.44</t>
+  </si>
+  <si>
+    <t>14:27:38.59</t>
+  </si>
+  <si>
+    <t>03:09:47.49</t>
+  </si>
+  <si>
+    <t>03:22:14.55</t>
+  </si>
+  <si>
+    <t>10:37:58.18</t>
+  </si>
+  <si>
+    <t>16:50:51.75</t>
+  </si>
+  <si>
+    <t>12:09:14.93</t>
+  </si>
+  <si>
+    <t>22:28:43.53</t>
+  </si>
+  <si>
+    <t>20:53:21.77</t>
+  </si>
+  <si>
+    <t>22:42:37.53</t>
+  </si>
+  <si>
+    <t>23:29:36.84</t>
+  </si>
+  <si>
+    <t>22:01:07.61</t>
+  </si>
+  <si>
+    <t>12:53:35.82</t>
+  </si>
+  <si>
+    <t>00:02:39.39</t>
+  </si>
+  <si>
+    <t>15:45:52.09</t>
+  </si>
+  <si>
+    <t>15:23:30.67</t>
+  </si>
+  <si>
+    <t>20:20:40.85</t>
+  </si>
+  <si>
+    <t>03:41:41.86</t>
+  </si>
+  <si>
+    <t>09:01:32.65</t>
+  </si>
+  <si>
+    <t>09:12:07.64</t>
+  </si>
+  <si>
+    <t>02:09:16.93</t>
+  </si>
+  <si>
+    <t>10:11:55.54</t>
+  </si>
+  <si>
+    <t>02:02:28.53</t>
+  </si>
+  <si>
+    <t>08:56:14.73</t>
+  </si>
+  <si>
+    <t>10:00:0.46</t>
+  </si>
+  <si>
+    <t>+18°42'48.71''</t>
+  </si>
+  <si>
+    <t>-31°13'46.00''</t>
+  </si>
+  <si>
+    <t>+31°38'34.20''</t>
+  </si>
+  <si>
+    <t>+48°14'31.20''</t>
+  </si>
+  <si>
+    <t>+54°47'17.70''</t>
+  </si>
+  <si>
+    <t>-06°05'30.65''</t>
+  </si>
+  <si>
+    <t>-35°21'04.13''</t>
+  </si>
+  <si>
+    <t>+33°12'41.93''</t>
+  </si>
+  <si>
+    <t>+27°17'57.31''</t>
+  </si>
+  <si>
+    <t>-18°41'17.48''</t>
+  </si>
+  <si>
+    <t>+40°33'28.74''</t>
+  </si>
+  <si>
+    <t>+54°57'01.38''</t>
+  </si>
+  <si>
+    <t>+53°27'48.05''</t>
+  </si>
+  <si>
+    <t>+01°10'31.91''</t>
+  </si>
+  <si>
+    <t>+00°47'06.80''</t>
+  </si>
+  <si>
+    <t>+03°34'22.03''</t>
+  </si>
+  <si>
+    <t>-15°20'14.46''</t>
+  </si>
+  <si>
+    <t>+23°38'37.95''</t>
+  </si>
+  <si>
+    <t>-02°46'55.29''</t>
+  </si>
+  <si>
+    <t>+25°50'34.96''</t>
+  </si>
+  <si>
+    <t>+60°28'23.95''</t>
+  </si>
+  <si>
+    <t>+29°35'39.67''</t>
+  </si>
+  <si>
+    <t>-62°15'09.36''</t>
+  </si>
+  <si>
+    <t>-00°48'12.70''</t>
+  </si>
+  <si>
+    <t>+16°15'06.84''</t>
+  </si>
+  <si>
+    <t>+66°58'46.95''</t>
+  </si>
+  <si>
+    <t>-56°26'50.44''</t>
+  </si>
+  <si>
+    <t>-01°30'52.69''</t>
+  </si>
+  <si>
+    <t>-17°08'27.75''</t>
+  </si>
+  <si>
+    <t>+02°23'59.60''</t>
+  </si>
+  <si>
+    <t>+02°22'56.20''</t>
   </si>
 </sst>
 </file>
@@ -290,11 +512,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normálna" xfId="0" builtinId="0"/>
@@ -629,17 +853,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.6328125" customWidth="1"/>
     <col min="3" max="3" width="13.90625" customWidth="1"/>
     <col min="4" max="4" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="17.54296875" customWidth="1"/>
-    <col min="8" max="8" width="15.36328125" customWidth="1"/>
+    <col min="5" max="5" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="17.54296875" customWidth="1"/>
+    <col min="10" max="10" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -653,21 +879,27 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F1" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="G1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>67</v>
       </c>
       <c r="B2">
-        <v>6.9964000000000004</v>
+        <v>6.9950000000000001</v>
       </c>
       <c r="C2">
         <v>3.5</v>
@@ -675,11 +907,17 @@
       <c r="D2">
         <v>0.21</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -692,11 +930,17 @@
       <c r="D3">
         <v>-0.86</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -709,11 +953,17 @@
       <c r="D4">
         <v>-1.31</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -727,16 +977,22 @@
         <v>-1.22</v>
       </c>
       <c r="E5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G5" t="s">
         <v>16</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>16</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>37</v>
       </c>
@@ -749,11 +1005,17 @@
       <c r="D6">
         <v>-0.98</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -766,17 +1028,23 @@
       <c r="D7">
         <v>-1.1200000000000001</v>
       </c>
-      <c r="E7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
+      <c r="E7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="G7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -790,16 +1058,22 @@
         <v>-0.16</v>
       </c>
       <c r="E8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G8" t="s">
         <v>14</v>
       </c>
-      <c r="F8" t="s">
+      <c r="H8" t="s">
         <v>16</v>
       </c>
-      <c r="G8" t="s">
+      <c r="I8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -811,13 +1085,19 @@
         <v>-0.67</v>
       </c>
       <c r="E9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G9" t="s">
         <v>48</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -827,11 +1107,17 @@
       <c r="D10">
         <v>-0.75</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G10" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -844,11 +1130,17 @@
       <c r="D11">
         <v>-1.04</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -860,13 +1152,19 @@
         <v>-0.94</v>
       </c>
       <c r="E12" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G12" t="s">
         <v>46</v>
       </c>
-      <c r="F12" t="s">
+      <c r="H12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -879,14 +1177,20 @@
       <c r="D13">
         <v>-0.44</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G13" t="s">
         <v>22</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -899,14 +1203,20 @@
       <c r="D14">
         <v>-0.61</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G14" t="s">
         <v>40</v>
       </c>
-      <c r="F14" t="s">
+      <c r="H14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -920,16 +1230,22 @@
         <v>0.06</v>
       </c>
       <c r="E15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G15" t="s">
         <v>16</v>
       </c>
-      <c r="F15" t="s">
+      <c r="H15" t="s">
         <v>16</v>
       </c>
-      <c r="G15" t="s">
+      <c r="I15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -940,13 +1256,19 @@
         <v>0.6</v>
       </c>
       <c r="E16" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G16" t="s">
         <v>16</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -960,10 +1282,16 @@
         <v>0.26</v>
       </c>
       <c r="E17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -974,13 +1302,19 @@
         <v>-0.39</v>
       </c>
       <c r="E18" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G18" t="s">
         <v>51</v>
       </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -991,13 +1325,19 @@
         <v>-0.75</v>
       </c>
       <c r="E19" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G19" t="s">
         <v>5</v>
       </c>
-      <c r="F19" t="s">
+      <c r="H19" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>44</v>
       </c>
@@ -1008,10 +1348,16 @@
         <v>-1.07</v>
       </c>
       <c r="E20" t="s">
+        <v>99</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G20" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1025,13 +1371,19 @@
         <v>-0.89</v>
       </c>
       <c r="E21" t="s">
+        <v>100</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G21" t="s">
         <v>10</v>
       </c>
-      <c r="F21" t="s">
+      <c r="H21" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -1045,33 +1397,45 @@
         <v>-0.51</v>
       </c>
       <c r="E22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G22" t="s">
         <v>16</v>
       </c>
-      <c r="F22" t="s">
+      <c r="H22" t="s">
         <v>16</v>
       </c>
-      <c r="G22" t="s">
+      <c r="I22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>25</v>
       </c>
       <c r="B23">
-        <v>5.82</v>
+        <v>5.774</v>
       </c>
       <c r="D23">
         <v>-1.22</v>
       </c>
       <c r="E23" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" t="s">
         <v>26</v>
       </c>
-      <c r="F23" t="s">
+      <c r="H23" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -1079,10 +1443,16 @@
         <v>5.8</v>
       </c>
       <c r="E24" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G24" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -1095,17 +1465,23 @@
       <c r="D25">
         <v>-1.6</v>
       </c>
-      <c r="E25" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" t="s">
-        <v>52</v>
+      <c r="E25" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="G25" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H25" t="s">
+        <v>52</v>
+      </c>
+      <c r="I25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>36</v>
       </c>
@@ -1119,16 +1495,22 @@
         <v>-0.79</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" t="s">
-        <v>54</v>
+        <v>104</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="G26" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H26" t="s">
+        <v>54</v>
+      </c>
+      <c r="I26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>32</v>
       </c>
@@ -1142,16 +1524,22 @@
         <v>-0.38</v>
       </c>
       <c r="E27" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" t="s">
-        <v>16</v>
+        <v>105</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="G27" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>59</v>
       </c>
@@ -1159,10 +1547,16 @@
         <v>5.718</v>
       </c>
       <c r="E28" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G28" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>20</v>
       </c>
@@ -1176,13 +1570,19 @@
         <v>-0.04</v>
       </c>
       <c r="E29" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G29" t="s">
         <v>14</v>
       </c>
-      <c r="F29" t="s">
+      <c r="H29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -1192,11 +1592,17 @@
       <c r="D30">
         <v>-0.75</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G30" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>8</v>
       </c>
@@ -1206,11 +1612,17 @@
       <c r="D31">
         <v>-0.75</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G31" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -1223,17 +1635,23 @@
       <c r="D32">
         <v>-0.23</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G32" t="s">
         <v>16</v>
       </c>
-      <c r="F32" t="s">
+      <c r="H32" t="s">
         <v>16</v>
       </c>
-      <c r="G32" t="s">
+      <c r="I32" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>60</v>
       </c>
@@ -1246,14 +1664,20 @@
       <c r="D33">
         <v>-0.27</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G33" t="s">
         <v>61</v>
       </c>
-      <c r="F33" t="s">
+      <c r="H33" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -1267,10 +1691,16 @@
         <v>-0.4</v>
       </c>
       <c r="E34" t="s">
+        <v>111</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G34" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>63</v>
       </c>
@@ -1283,11 +1713,17 @@
       <c r="D35">
         <v>-0.65</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G35" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>68</v>
       </c>
@@ -1300,11 +1736,17 @@
       <c r="D36">
         <v>-1.18</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G36" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>70</v>
       </c>
@@ -1315,11 +1757,17 @@
         <v>-1.68</v>
       </c>
       <c r="E37" t="s">
+        <v>114</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G37" t="s">
         <v>71</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G33">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I33">
     <sortCondition descending="1" ref="B1:B33"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/datasets/radio_sources_EoR.xlsx
+++ b/datasets/radio_sources_EoR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tomas\Documents\astrophysics\website\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD83C3D8-B049-4BEF-AB9D-8D15856B6EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9631EBD-1250-454F-8987-5B7D09CE0780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hárok1" sheetId="1" r:id="rId1"/>
@@ -1414,68 +1414,74 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B23">
-        <v>5.774</v>
-      </c>
-      <c r="D23">
-        <v>-1.22</v>
+        <v>5.8</v>
       </c>
       <c r="E23" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="G23" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>5.8</v>
       </c>
-      <c r="E24" t="s">
-        <v>102</v>
+      <c r="C24">
+        <v>1.29</v>
+      </c>
+      <c r="D24">
+        <v>-1.6</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G24" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="H24" t="s">
+        <v>52</v>
+      </c>
+      <c r="I24" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B25">
-        <v>5.8</v>
+        <v>5.78</v>
       </c>
       <c r="C25">
-        <v>1.29</v>
+        <v>0.86</v>
       </c>
       <c r="D25">
-        <v>-1.6</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>103</v>
+        <v>-0.79</v>
+      </c>
+      <c r="E25" t="s">
+        <v>104</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G25" t="s">
         <v>17</v>
       </c>
       <c r="H25" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I25" t="s">
         <v>17</v>
@@ -1483,31 +1489,25 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B26">
-        <v>5.78</v>
-      </c>
-      <c r="C26">
-        <v>0.86</v>
+        <v>5.774</v>
       </c>
       <c r="D26">
-        <v>-0.79</v>
+        <v>-1.22</v>
       </c>
       <c r="E26" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="G26" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H26" t="s">
-        <v>54</v>
-      </c>
-      <c r="I26" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">

--- a/datasets/radio_sources_EoR.xlsx
+++ b/datasets/radio_sources_EoR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tomas\Documents\astrophysics\website\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9631EBD-1250-454F-8987-5B7D09CE0780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EDB55EA-287C-47D1-8BD0-AF9EF4E86C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38295" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hárok1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="153">
   <si>
     <t>name</t>
   </si>
@@ -477,6 +477,27 @@
   </si>
   <si>
     <t>+02°22'56.20''</t>
+  </si>
+  <si>
+    <t>EUCL J0933</t>
+  </si>
+  <si>
+    <t>09:33:30.60</t>
+  </si>
+  <si>
+    <t>+74°27'30.00'</t>
+  </si>
+  <si>
+    <t>Yang+26</t>
+  </si>
+  <si>
+    <t>EUCL J0916</t>
+  </si>
+  <si>
+    <t>09:16:39.93</t>
+  </si>
+  <si>
+    <t>+68°25'52.90"</t>
   </si>
 </sst>
 </file>
@@ -853,19 +874,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I37"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I39"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.6328125" customWidth="1"/>
-    <col min="3" max="3" width="13.90625" customWidth="1"/>
-    <col min="4" max="4" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="17.54296875" customWidth="1"/>
-    <col min="10" max="10" width="15.36328125" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="4" max="4" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="17.5703125" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -894,7 +915,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -917,858 +938,898 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3">
+        <v>6.96</v>
+      </c>
+      <c r="C3">
+        <v>0.49</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B4" s="1">
         <v>6.8529999999999998</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>0.47499999999999998</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>-0.86</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B5" s="1">
         <v>6.82</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D4">
+      <c r="D5">
         <v>-1.31</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="1">
+        <v>6.6</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>28</v>
       </c>
-      <c r="B5">
+      <c r="B7">
         <v>6.6</v>
       </c>
-      <c r="C5">
+      <c r="C7">
         <v>1.38</v>
       </c>
-      <c r="D5">
+      <c r="D7">
         <v>-1.22</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E7" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G7" t="s">
         <v>16</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H7" t="s">
         <v>16</v>
-      </c>
-      <c r="I5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="1">
-        <v>6.44</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6">
-        <v>-0.98</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7">
-        <v>6.38</v>
-      </c>
-      <c r="C7">
-        <v>1.27</v>
-      </c>
-      <c r="D7">
-        <v>-1.1200000000000001</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" t="s">
-        <v>53</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="1">
+        <v>6.44</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8">
+        <v>-0.98</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9">
+        <v>6.38</v>
+      </c>
+      <c r="C9">
+        <v>1.27</v>
+      </c>
+      <c r="D9">
+        <v>-1.1200000000000001</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>15</v>
       </c>
-      <c r="B8">
+      <c r="B10">
         <v>6.2329999999999997</v>
       </c>
-      <c r="C8">
+      <c r="C10">
         <v>4.6580000000000004</v>
       </c>
-      <c r="D8">
+      <c r="D10">
         <v>-0.16</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E10" t="s">
         <v>87</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G10" t="s">
         <v>14</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H10" t="s">
         <v>16</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B11" s="1">
         <v>6.21</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9">
+      <c r="C11" s="1"/>
+      <c r="D11">
         <v>-0.67</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E11" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G11" t="s">
         <v>48</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H11" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B12" s="1">
         <v>6.2</v>
       </c>
-      <c r="D10">
+      <c r="D12">
         <v>-0.75</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B13" s="1">
         <v>6.13</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D11">
+      <c r="D13">
         <v>-1.04</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B14" s="1">
         <v>6.12</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12">
+      <c r="C14" s="1"/>
+      <c r="D14">
         <v>-0.94</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E14" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G14" t="s">
         <v>46</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B15" s="1">
         <v>6.1</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C15" s="1">
         <v>64.2</v>
       </c>
-      <c r="D13">
+      <c r="D15">
         <v>-0.44</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G15" t="s">
         <v>22</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B16" s="1">
         <v>6.09</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D14">
+      <c r="D16">
         <v>-0.61</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G16" t="s">
         <v>40</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>29</v>
       </c>
-      <c r="B15">
+      <c r="B17">
         <v>6.07</v>
       </c>
-      <c r="C15">
+      <c r="C17">
         <v>8.17</v>
       </c>
-      <c r="D15">
+      <c r="D17">
         <v>0.06</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E17" t="s">
         <v>94</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G17" t="s">
         <v>16</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H17" t="s">
         <v>16</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>30</v>
       </c>
-      <c r="B16">
+      <c r="B18">
         <v>6.06</v>
       </c>
-      <c r="C16">
+      <c r="C18">
         <v>0.6</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E18" t="s">
         <v>95</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G18" t="s">
         <v>16</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H18" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B17">
+      <c r="B19">
         <v>5.99</v>
       </c>
-      <c r="C17">
+      <c r="C19">
         <v>0.24099999999999999</v>
       </c>
-      <c r="D17">
+      <c r="D19">
         <v>0.26</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E19" t="s">
         <v>96</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>50</v>
       </c>
-      <c r="B18">
+      <c r="B20">
         <v>5.95</v>
       </c>
-      <c r="D18">
+      <c r="D20">
         <v>-0.39</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E20" t="s">
         <v>97</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G20" t="s">
         <v>51</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H20" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>4</v>
       </c>
-      <c r="B19">
+      <c r="B21">
         <v>5.92</v>
       </c>
-      <c r="D19">
+      <c r="D21">
         <v>-0.75</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E21" t="s">
         <v>98</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G21" t="s">
         <v>5</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H21" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B22" s="1">
         <v>5.88</v>
       </c>
-      <c r="D20">
+      <c r="D22">
         <v>-1.07</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E22" t="s">
         <v>99</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G22" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B23" s="1">
         <v>5.84</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C23" s="1">
         <v>110.6</v>
       </c>
-      <c r="D21">
+      <c r="D23">
         <v>-0.89</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E23" t="s">
         <v>100</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G23" t="s">
         <v>10</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H23" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>31</v>
       </c>
-      <c r="B22">
+      <c r="B24">
         <v>5.83</v>
       </c>
-      <c r="C22">
+      <c r="C24">
         <v>3.56</v>
       </c>
-      <c r="D22">
+      <c r="D24">
         <v>-0.51</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E24" t="s">
         <v>101</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G24" t="s">
         <v>16</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H24" t="s">
         <v>16</v>
-      </c>
-      <c r="I22" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23">
-        <v>5.8</v>
-      </c>
-      <c r="E23" t="s">
-        <v>102</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24">
-        <v>5.8</v>
-      </c>
-      <c r="C24">
-        <v>1.29</v>
-      </c>
-      <c r="D24">
-        <v>-1.6</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G24" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24" t="s">
-        <v>52</v>
       </c>
       <c r="I24" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25">
+        <v>5.8</v>
+      </c>
+      <c r="E25" t="s">
+        <v>102</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26">
+        <v>5.8</v>
+      </c>
+      <c r="C26">
+        <v>1.29</v>
+      </c>
+      <c r="D26">
+        <v>-1.6</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G26" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" t="s">
+        <v>52</v>
+      </c>
+      <c r="I26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>36</v>
       </c>
-      <c r="B25">
+      <c r="B27">
         <v>5.78</v>
       </c>
-      <c r="C25">
+      <c r="C27">
         <v>0.86</v>
       </c>
-      <c r="D25">
+      <c r="D27">
         <v>-0.79</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E27" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G27" t="s">
         <v>17</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H27" t="s">
         <v>54</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I27" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>25</v>
       </c>
-      <c r="B26">
+      <c r="B28">
         <v>5.774</v>
       </c>
-      <c r="D26">
+      <c r="D28">
         <v>-1.22</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E28" t="s">
         <v>81</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G28" t="s">
         <v>26</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H28" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>32</v>
       </c>
-      <c r="B27">
+      <c r="B29">
         <v>5.74</v>
       </c>
-      <c r="C27">
+      <c r="C29">
         <v>1.3</v>
       </c>
-      <c r="D27">
+      <c r="D29">
         <v>-0.38</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E29" t="s">
         <v>105</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F29" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G29" t="s">
         <v>16</v>
-      </c>
-      <c r="H27" t="s">
-        <v>16</v>
-      </c>
-      <c r="I27" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="1">
-        <v>5.718</v>
-      </c>
-      <c r="E28" t="s">
-        <v>106</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B29">
-        <v>5.69</v>
-      </c>
-      <c r="C29">
-        <v>0.48499999999999999</v>
-      </c>
-      <c r="D29">
-        <v>-0.04</v>
-      </c>
-      <c r="E29" t="s">
-        <v>79</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G29" t="s">
-        <v>14</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="I29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="1">
+        <v>5.718</v>
+      </c>
+      <c r="E30" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31">
+        <v>5.69</v>
+      </c>
+      <c r="C31">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="D31">
+        <v>-0.04</v>
+      </c>
+      <c r="E31" t="s">
+        <v>79</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G31" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>7</v>
       </c>
-      <c r="B30">
+      <c r="B32">
         <v>5.68</v>
       </c>
-      <c r="D30">
+      <c r="D32">
         <v>-0.75</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G32" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>8</v>
       </c>
-      <c r="B31">
+      <c r="B33">
         <v>5.63</v>
       </c>
-      <c r="D31">
+      <c r="D33">
         <v>-0.75</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G33" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>33</v>
       </c>
-      <c r="B32">
+      <c r="B34">
         <v>5.62</v>
       </c>
-      <c r="C32">
+      <c r="C34">
         <v>1.22</v>
       </c>
-      <c r="D32">
+      <c r="D34">
         <v>-0.23</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G34" t="s">
         <v>16</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H34" t="s">
         <v>16</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I34" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B35" s="1">
         <v>5.6059999999999999</v>
       </c>
-      <c r="C33">
+      <c r="C35">
         <v>29.5</v>
       </c>
-      <c r="D33">
+      <c r="D35">
         <v>-0.27</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G35" t="s">
         <v>61</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H35" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>62</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B36" s="1">
         <v>5.58</v>
       </c>
-      <c r="C34">
+      <c r="C36">
         <v>7.46</v>
       </c>
-      <c r="D34">
+      <c r="D36">
         <v>-0.4</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E36" t="s">
         <v>111</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F36" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G36" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>63</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B37" s="1">
         <v>5.57</v>
       </c>
-      <c r="C35">
+      <c r="C37">
         <v>43.16</v>
       </c>
-      <c r="D35">
+      <c r="D37">
         <v>-0.65</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F37" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G37" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B38" s="1">
         <v>5.55</v>
       </c>
-      <c r="C36">
+      <c r="C38">
         <v>899.82</v>
       </c>
-      <c r="D36">
+      <c r="D38">
         <v>-1.18</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F38" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G38" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B39" s="1">
         <v>5.5446999999999997</v>
       </c>
-      <c r="D37">
+      <c r="D39">
         <v>-1.68</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E39" t="s">
         <v>114</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F39" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G39" t="s">
         <v>71</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I33">
-    <sortCondition descending="1" ref="B1:B33"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:I35">
+    <sortCondition descending="1" ref="B1:B35"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/datasets/radio_sources_EoR.xlsx
+++ b/datasets/radio_sources_EoR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tomas\Documents\astrophysics\website\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EDB55EA-287C-47D1-8BD0-AF9EF4E86C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2344D61-256B-4B54-816E-6EB2E68910DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="-1560" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hárok1" sheetId="1" r:id="rId1"/>
@@ -485,9 +485,6 @@
     <t>09:33:30.60</t>
   </si>
   <si>
-    <t>+74°27'30.00'</t>
-  </si>
-  <si>
     <t>Yang+26</t>
   </si>
   <si>
@@ -498,6 +495,9 @@
   </si>
   <si>
     <t>+68°25'52.90"</t>
+  </si>
+  <si>
+    <t>+74°27'30.00''</t>
   </si>
 </sst>
 </file>
@@ -952,10 +952,10 @@
         <v>147</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" t="s">
         <v>148</v>
-      </c>
-      <c r="G3" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1006,7 +1006,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B6" s="1">
         <v>6.6</v>
@@ -1015,13 +1015,13 @@
         <v>1.53</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="G6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">

--- a/datasets/radio_sources_EoR.xlsx
+++ b/datasets/radio_sources_EoR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tomas\Documents\astrophysics\website\datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2344D61-256B-4B54-816E-6EB2E68910DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869A41F3-4A38-4D63-BE05-17D63E0B5C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25710" yWindow="-1560" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -494,10 +494,10 @@
     <t>09:16:39.93</t>
   </si>
   <si>
-    <t>+68°25'52.90"</t>
-  </si>
-  <si>
     <t>+74°27'30.00''</t>
+  </si>
+  <si>
+    <t>+68°25'52.90''</t>
   </si>
 </sst>
 </file>
@@ -952,7 +952,7 @@
         <v>147</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G3" t="s">
         <v>148</v>
@@ -1018,7 +1018,7 @@
         <v>150</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G6" t="s">
         <v>148</v>
